--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:43</t>
+    <t xml:space="preserve">2026-09-09 22:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:30</t>
+    <t xml:space="preserve">2026-09-12 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los rios.xlsx
@@ -42,27 +42,27 @@
     <t xml:space="preserve">Panguipulli</t>
   </si>
   <si>
+    <t xml:space="preserve">Los Lagos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Unión</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mariquina</t>
   </si>
   <si>
+    <t xml:space="preserve">Futrono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paillaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lanco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lago Ranco</t>
   </si>
   <si>
-    <t xml:space="preserve">La Unión</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Futrono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Lagos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paillaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lanco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Máfil</t>
   </si>
   <si>
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:46</t>
+    <t xml:space="preserve">2026-09-24 00:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -511,7 +511,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4763</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="3">
@@ -528,7 +528,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2752</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="4">
@@ -539,13 +539,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>14106</v>
+        <v>14104</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1829</v>
+        <v>892</v>
       </c>
     </row>
     <row r="5">
@@ -556,13 +556,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>14203</v>
+        <v>14201</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1594</v>
+        <v>794</v>
       </c>
     </row>
     <row r="6">
@@ -573,13 +573,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>14201</v>
+        <v>14106</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1198</v>
+        <v>753</v>
       </c>
     </row>
     <row r="7">
@@ -596,7 +596,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1148</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8">
@@ -607,13 +607,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>14104</v>
+        <v>14107</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1092</v>
+        <v>706</v>
       </c>
     </row>
     <row r="9">
@@ -624,13 +624,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>14107</v>
+        <v>14103</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1076</v>
+        <v>547</v>
       </c>
     </row>
     <row r="10">
@@ -641,13 +641,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>14103</v>
+        <v>14203</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>910</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11">
@@ -664,7 +664,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>187</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12">
@@ -681,7 +681,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-14</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -698,7 +698,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-1386</v>
+        <v>-134</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:24</t>
+    <t xml:space="preserve">2026-09-27 22:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:13</t>
+    <t xml:space="preserve">2026-10-01 20:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:53</t>
+    <t xml:space="preserve">2026-10-02 13:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:24</t>
+    <t xml:space="preserve">2026-10-05 08:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
